--- a/data/trans_bre/IP19C03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 12,78</t>
+          <t>-7,79; 12,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 2,65</t>
+          <t>-20,54; 1,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 18,77</t>
+          <t>-4,19; 16,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 15,59</t>
+          <t>-4,83; 15,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,37; 92,08</t>
+          <t>-32,68; 91,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 12,88</t>
+          <t>-67,99; 9,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 177,97</t>
+          <t>-22,24; 148,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 230,01</t>
+          <t>-31,81; 214,97</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 16,61</t>
+          <t>-1,47; 16,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 14,19</t>
+          <t>-5,63; 12,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 5,44</t>
+          <t>-12,11; 6,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 3,11</t>
+          <t>-12,92; 2,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 113,53</t>
+          <t>-7,1; 111,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 75,09</t>
+          <t>-20,3; 62,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 31,17</t>
+          <t>-44,38; 36,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,13; 22,59</t>
+          <t>-60,54; 20,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 15,99</t>
+          <t>-4,91; 15,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 7,7</t>
+          <t>-14,14; 6,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 2,4</t>
+          <t>-18,23; 2,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 19,11</t>
+          <t>-1,59; 20,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 133,11</t>
+          <t>-23,58; 142,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 48,73</t>
+          <t>-52,94; 37,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,92; 15,1</t>
+          <t>-63,24; 15,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 144,77</t>
+          <t>-8,82; 161,74</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 5,8</t>
+          <t>-11,97; 6,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 17,75</t>
+          <t>1,0; 17,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 6,74</t>
+          <t>-7,24; 7,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 6,26</t>
+          <t>-9,7; 6,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 50,35</t>
+          <t>-55,42; 49,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 300,31</t>
+          <t>2,24; 297,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 83,76</t>
+          <t>-49,4; 102,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 63,43</t>
+          <t>-52,92; 68,21</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 7,87</t>
+          <t>-1,19; 8,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 6,02</t>
+          <t>-3,85; 6,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,43</t>
+          <t>-6,27; 3,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,07</t>
+          <t>-3,22; 6,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 51,36</t>
+          <t>-5,77; 55,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 36,2</t>
+          <t>-17,58; 36,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 22,16</t>
+          <t>-29,57; 19,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 43,57</t>
+          <t>-17,46; 46,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 12,77</t>
+          <t>-7,89; 12,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 1,42</t>
+          <t>-19,7; 2,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 16,41</t>
+          <t>-3,63; 17,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 15,98</t>
+          <t>-4,99; 16,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 91,91</t>
+          <t>-34,32; 92,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 9,82</t>
+          <t>-63,92; 13,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 148,35</t>
+          <t>-19,23; 166,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 214,97</t>
+          <t>-28,3; 222,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 16,65</t>
+          <t>-1,46; 16,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 12,56</t>
+          <t>-5,32; 13,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 6,68</t>
+          <t>-11,22; 6,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 2,65</t>
+          <t>-12,95; 1,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 111,46</t>
+          <t>-4,24; 118,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 62,61</t>
+          <t>-19,0; 71,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 36,01</t>
+          <t>-41,99; 35,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,54; 20,74</t>
+          <t>-60,77; 14,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 15,24</t>
+          <t>-4,26; 15,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 6,13</t>
+          <t>-13,05; 6,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 2,37</t>
+          <t>-17,85; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 20,44</t>
+          <t>-1,98; 19,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 142,32</t>
+          <t>-20,9; 135,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,94; 37,97</t>
+          <t>-51,3; 37,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,24; 15,96</t>
+          <t>-59,63; 25,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 161,74</t>
+          <t>-11,7; 152,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 6,41</t>
+          <t>-11,3; 5,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 17,38</t>
+          <t>1,41; 17,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 7,75</t>
+          <t>-7,52; 6,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 6,51</t>
+          <t>-11,02; 7,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 49,83</t>
+          <t>-54,15; 47,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 297,14</t>
+          <t>1,46; 292,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 102,41</t>
+          <t>-53,59; 83,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 68,21</t>
+          <t>-57,43; 74,74</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,08</t>
+          <t>-1,11; 8,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 6,07</t>
+          <t>-3,58; 5,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 3,18</t>
+          <t>-5,9; 3,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 6,53</t>
+          <t>-3,75; 6,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 55,01</t>
+          <t>-5,84; 53,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 36,25</t>
+          <t>-15,87; 33,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 19,71</t>
+          <t>-28,37; 19,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 46,99</t>
+          <t>-19,62; 43,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 12,45</t>
+          <t>-7,85; 12,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 2,11</t>
+          <t>-18,98; 2,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 17,58</t>
+          <t>-2,53; 18,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 16,03</t>
+          <t>-4,87; 15,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 92,67</t>
+          <t>-35,37; 92,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 13,77</t>
+          <t>-65,03; 12,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 166,75</t>
+          <t>-16,31; 177,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 222,42</t>
+          <t>-33,86; 211,63</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,3</t>
+          <t>-4,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-28,99%</t>
+          <t>-27,37%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 16,2</t>
+          <t>-0,29; 16,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 13,3</t>
+          <t>-4,32; 14,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 6,53</t>
+          <t>-12,32; 5,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 1,99</t>
+          <t>-12,54; 3,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 118,04</t>
+          <t>-2,1; 113,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 71,63</t>
+          <t>-15,97; 75,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 35,52</t>
+          <t>-41,2; 31,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 14,9</t>
+          <t>-59,58; 26,36</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 15,89</t>
+          <t>-3,92; 15,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 6,01</t>
+          <t>-13,8; 7,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 3,99</t>
+          <t>-18,92; 2,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 19,68</t>
+          <t>-3,75; 16,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 135,03</t>
+          <t>-20,48; 133,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 37,52</t>
+          <t>-53,24; 48,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,63; 25,02</t>
+          <t>-61,92; 15,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 152,05</t>
+          <t>-17,51; 125,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-9,19%</t>
+          <t>-0,5%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 5,84</t>
+          <t>-12,13; 5,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 17,07</t>
+          <t>1,39; 17,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 6,54</t>
+          <t>-7,34; 6,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 7,29</t>
+          <t>-8,56; 7,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 47,88</t>
+          <t>-55,37; 50,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 292,12</t>
+          <t>4,7; 300,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,59; 83,55</t>
+          <t>-51,62; 83,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 74,74</t>
+          <t>-51,01; 79,41</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,28</t>
+          <t>-1,56; 7,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,76</t>
+          <t>-3,68; 6,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,11</t>
+          <t>-5,63; 3,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 6,28</t>
+          <t>-3,43; 5,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 53,74</t>
+          <t>-8,24; 51,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 33,59</t>
+          <t>-16,24; 36,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 19,42</t>
+          <t>-26,95; 22,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 43,85</t>
+          <t>-19,66; 40,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-8,69</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,51</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-36,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44,92%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.46562846920716</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-8.692012946475428</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6.511000595705243</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.643522176483831</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1360447690626495</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3611993421547409</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.424078911037046</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.4492117322242319</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,85; 12,78</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-18,98; 2,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,53; 18,77</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,87; 15,12</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-35,37; 92,08</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-65,03; 12,88</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-16,31; 177,97</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-33,86; 211,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.85484644335752</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-18.98279198288082</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.53076034824046</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.867231741542434</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3537205998131909</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.6503153287544305</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1631375061103066</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3385880945333946</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.78400540500744</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.646619527932148</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>18.76707036320889</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>15.12034910389052</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.9207693219066847</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.12884211401531</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.779709915195168</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.116295211257138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7,62</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,42</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,52</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>40,94%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-10,91%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-27,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,29; 16,61</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,32; 14,19</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-12,32; 5,44</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-12,54; 3,27</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 113,53</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-15,97; 75,09</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-41,2; 31,17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-59,58; 26,36</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>7.616861010852655</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.418082468715107</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.515452222883835</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.804311351504073</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.4093749381949571</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1883885642323118</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1090881407569987</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2737298913270582</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,73</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,63</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-17,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-32,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37,49%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.2949929903206679</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.321787963953026</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-12.32208135450227</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-12.53787937431565</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.0209558290360527</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1596651871552113</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4119701487220384</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5958392108451385</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,92; 15,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-13,8; 7,7</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-18,92; 2,4</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 16,4</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-20,48; 133,11</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-53,24; 48,73</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-61,92; 15,1</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-17,51; 125,3</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>16.6055378057231</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>14.18671607325786</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.439712922658409</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.266361351386569</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.135298925968145</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.7509479787871628</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.3117423004447563</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2636250213078742</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9,26</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-18,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,92%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-0,5%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.672700688792654</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.733245986524347</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-7.630403717767351</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6.717745908313893</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3505586267537809</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1750621632674802</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3228035903562942</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.3749031707289137</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-12,13; 5,8</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 17,75</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,34; 6,74</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,56; 7,49</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-55,37; 50,35</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,7; 300,31</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-51,62; 83,76</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-51,01; 79,41</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.917880661403738</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-13.80035794703969</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-18.92170558400711</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.746466361738125</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2048301676749434</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5323998529288508</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6191581728056983</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1751046157378469</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>15.99409099663926</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.696078867365442</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.395980474333906</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>16.4049764049611</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.331084874157289</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.4872704045054112</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1510184271708543</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.252981780859811</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.111295894043375</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>9.26140391451063</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3312252188324941</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.06621847746065002</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1842541033272428</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.9942115740834513</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.02915423430116594</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.004955311552177199</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-12.13019012739007</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.394703933727398</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.34048987960762</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.561427676623417</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5536850564501138</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.04695411799380318</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5162006733026</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5101151035982878</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.803791785668069</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>17.74958086136374</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.744227812634547</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.492869932865285</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.503538474993251</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.003143185196248</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.837588314599656</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.7940951093066755</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-6,58%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,56; 7,87</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,68; 6,02</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,63; 3,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 5,54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-8,24; 51,36</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-16,24; 36,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-26,95; 22,16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-19,66; 40,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>3.195259145257123</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.242244785383304</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.197430948146572</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.182347233879991</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1821031286744006</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.06402929473860157</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.06581632759428456</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.07481427292244748</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.563120393880569</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.677277002867448</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.628604645530022</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.430634351798952</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.08241125215799043</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1624184683845573</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2694787922735372</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1966384700889748</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.866137563631765</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.019567994140757</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.433660951318086</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.537416335800693</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5135953675968137</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3620196931720713</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.221639448007089</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.4004741970520224</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
